--- a/Output/PowerPoint_Figures/Fig_6/Fig_6g_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_6/Fig_6g_data.xlsx
@@ -22,16 +22,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -50,21 +47,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +422,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ROC_AUC</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>AUC_Mean</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AUC_Std</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -477,7 +465,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\comparison_metrics_all.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/comparison_metrics_all.csv</t>
         </is>
       </c>
     </row>
@@ -498,7 +486,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\comparison_metrics_all.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/comparison_metrics_all.csv</t>
         </is>
       </c>
     </row>
@@ -519,7 +507,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\comparison_metrics_all.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/comparison_metrics_all.csv</t>
         </is>
       </c>
     </row>
@@ -538,22 +526,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>FPR</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TPR</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -2174,22 +2162,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>FPR</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TPR</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3810,22 +3798,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>FPR</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TPR</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -5446,27 +5434,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Drug</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Arrhythmia_label</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CNN_25_prob</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CNN_25_pred</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -5489,7 +5477,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5498,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5519,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5540,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5561,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5582,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5603,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5624,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5645,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5666,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5687,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5708,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5729,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5750,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5771,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5792,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5813,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5834,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5867,7 +5855,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5876,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5897,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5918,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5939,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5960,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5981,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_cnn_25drugs_cv.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_cnn_25drugs_cv.csv</t>
         </is>
       </c>
     </row>
@@ -6012,27 +6000,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Drug</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Arrhythmia_label</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>DIQT_prob</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DIQT_pred</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -6055,7 +6043,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6064,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6085,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6106,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6127,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6148,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6169,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6190,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6223,7 +6211,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6232,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6253,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6274,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6295,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6316,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6337,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6358,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6379,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6400,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6421,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6442,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6463,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6484,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6505,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6526,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6547,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\MoLFormer_Comparison\molformer_predictions_25.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/MoLFormer_Comparison/molformer_predictions_25.csv</t>
         </is>
       </c>
     </row>
